--- a/output/pdf_financials_xlsx/SKNY.xlsx
+++ b/output/pdf_financials_xlsx/SKNY.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.217155</v>
+        <v>-1.217155</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-4.337197</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.217155</v>
+        <v>-1.217155</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-4.337197</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.217155</v>
+        <v>-1.217155</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-4.337197</v>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>30.428875</v>
+        <v>-30.428875</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>5.941366</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.217155</v>
+        <v>-1.217155</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-4.337197</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.217155</v>
+        <v>-1.217155</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-4.337197</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.489379</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.453795</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.490554</v>
       </c>
     </row>
     <row r="93">
@@ -3092,7 +3092,11 @@
           <t>Reserves (Notes 9)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3429,7 +3433,11 @@
           <t>Reserves (Notes 11)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.489379</v>
       </c>
@@ -5783,10 +5791,10 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1.217155</v>
+        <v>-1.217155</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>4.337197</v>
+        <v>-4.337197</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SKNY.xlsx
+++ b/output/pdf_financials_xlsx/SKNY.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.123521</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.07592400000000001</v>
       </c>
     </row>
     <row r="13">
@@ -864,10 +864,10 @@
         <v>-1.217155</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.337197</v>
+        <v>-4.460718</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.358122</v>
+        <v>-7.434046</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-1.217155</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.337197</v>
+        <v>-4.460718</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.358122</v>
+        <v>-7.434046</v>
       </c>
     </row>
     <row r="30">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">

--- a/output/pdf_financials_xlsx/SKNY.xlsx
+++ b/output/pdf_financials_xlsx/SKNY.xlsx
@@ -4630,7 +4630,11 @@
           <t>Proceeds received in advance of 2024 Private Placement</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>0.523407</v>
       </c>
